--- a/EstablecimientoSalud/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
+++ b/EstablecimientoSalud/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>35683</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.6990365</t>
+          <t>-6.7061836</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.9076147</t>
+          <t>-79.9136223</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CONSULTORIO MILAGRITOS SALUD</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO NAYLAMP LAMBAYEQUE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CALLE CALLE LIBERTAD Nº 620 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+          <t>AVENIDA FERNANDO BELAUNDE TERRY NUMERO 140 MANZANA A LOTE 4 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>35683</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,32 +642,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.7061836</t>
+          <t>-6.70073667</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.9136223</t>
+          <t>-79.91441167</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO NAYLAMP LAMBAYEQUE</t>
+          <t>CENTRO DE SALUD SAN MARTIN-LAMBAYEQUE</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AVENIDA FERNANDO BELAUNDE TERRY NUMERO 140 MANZANA A LOTE 4 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+          <t>CALLE CALLE SAN ANTONIO Nº 299 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>36414</t>
+          <t>25198</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.69765389</t>
+          <t>-6.70213204</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.90363029</t>
+          <t>-79.91085983</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO SANTO TOMAS PERU</t>
+          <t>CENTRO MEDICO MILITAR "DIVINO NIAO DEL MILAGRO DE ETEN"</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AVENIDA HUAMACHUCO NUMERO 181 MANZANA 23 LOTE 2 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+          <t>CALLE GRAU NUMERO S/N DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>31843</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.70073667</t>
+          <t>-6.7197666</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.91441167</t>
+          <t>-79.9080757</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD SAN MARTIN-LAMBAYEQUE</t>
+          <t>CENTRO MEDICO DE  LA SOCIEDAD DE BENEFICENCIA DE LAMBAYEQUE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CALLE CALLE SAN ANTONIO Nº 299 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+          <t>CALLE JUNIN NUMERO 576 PISO 1 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28903</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.705711</t>
+          <t>-6.64515609</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.912285</t>
+          <t>-79.91956345</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CENTRO CLINICO LAMBAYEQUE</t>
+          <t>PUESTO DE SALUD MUYFINCA-PUNTO 09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CALLE CIRO ALEGRIA PISO 1 MANZANA A LOTE 21 URBANIZACION LA REPUBLICANA DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+          <t>OTROS C.P MUY FINCA PUNTO 9 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>32807</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.7197666</t>
+          <t>-6.626905</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.9080757</t>
+          <t>-79.86521667</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO AMISTAD Y SALUD</t>
+          <t>SIALUPE HUAMANTANGA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AVENIDA LUIS GONZALES NUMERO 261 PISO 2 DISTRITO CHICLAYO PROVINCIA CHICLAYO DEPARTAMENTO LAMBAYEQUE</t>
+          <t>OTROS CAS.SIALUPE HUAMANTANGA/SECTOR LOS MESTAS DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,32 +952,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.70213204</t>
+          <t>-6.69581039</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.91085983</t>
+          <t>-79.90944934</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO MILITAR "DIVINO NIAO DEL MILAGRO DE ETEN"</t>
+          <t>TORIBIA CASTRO CHIRINOS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CALLE GRAU NUMERO S/N DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+          <t>CALLE CALLE ANDRRES AVELINO CACERES 489 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,27 +1014,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.7197666</t>
+          <t>-6.7378879</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.9080757</t>
+          <t>-79.95620034</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO DE  LA SOCIEDAD DE BENEFICENCIA DE LAMBAYEQUE</t>
+          <t>BODEGONES</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CALLE JUNIN NUMERO 576 PISO 1 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+          <t>OTROS CASERIO BODEGONES CASERIO BODEGONES SAN JOSE LAMBAYEQUE LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.64515609</t>
+          <t>-6.72087641</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.91956345</t>
+          <t>-79.97555329</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD MUYFINCA-PUNTO 09</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OTROS C.P MUY FINCA PUNTO 9 DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+          <t>OTROS CASERIO SAN CARLOS CASERIO SAN CARLOS SAN JOSE LAMBAYEQUE LAMBAYEQUE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1105,6 +1105,130 @@
         </is>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>140301</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12241</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-6.7035516</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-79.9018066</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AGUSTIN GAVIDIA SALCEDO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CALLE CALLE POEMAPE Nº 120 - LAMBAYEQUE DISTRITO LAMBAYEQUE PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>140301</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-6.59569656</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-79.87627009</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PUNTO CUATRO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OTROS CENTRO POBLADO PUNTO CUATRO DISTRITO MOCHUMI PROVINCIA LAMBAYEQUE DEPARTAMENTO LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>140301</t>
         </is>

--- a/EstablecimientoSalud/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
+++ b/EstablecimientoSalud/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>4377</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>140312</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TUCUME</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-6.47903</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>35683</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-6.7061836</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>4372</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-6.70073667</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>25198</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-6.70213204</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>31843</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-6.7197666</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>4375</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-6.64515609</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>4374</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-6.626905</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>4373</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-6.69581039</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>4347</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-6.7378879</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>4346</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-6.72087641</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>12241</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-6.7035516</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>4382</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-6.59569656</t>
@@ -1226,11 +1166,6 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>140301</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
+++ b/EstablecimientoSalud/excels/LAMBAYEQUE-LAMBAYEQUE-LAMBAYEQUE.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
